--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
@@ -1218,11 +1218,7 @@
           <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
@@ -1523,11 +1519,7 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>MUEBLES ANDROMEDA DOS SPA</t>
@@ -1754,7 +1746,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2133,11 +2125,7 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>JAIME DEIK Y CIA. LIMITADA</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1229,7 +1253,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1290,7 +1318,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1351,7 +1383,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1473,7 +1509,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1530,7 +1570,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1652,7 +1696,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1713,7 +1761,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1774,7 +1826,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1835,7 +1891,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2018,7 +2078,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2079,7 +2143,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2025.xlsx
@@ -1242,7 +1242,11 @@
           <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
@@ -1559,7 +1563,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>MUEBLES ANDROMEDA DOS SPA</t>
@@ -1798,7 +1806,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2193,7 +2201,11 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>JAIME DEIK Y CIA. LIMITADA</t>
